--- a/public/plantilla-com-pendientes.xlsx
+++ b/public/plantilla-com-pendientes.xlsx
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -196,7 +196,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -294,6 +294,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6FAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -599,7 +604,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
@@ -724,34 +729,34 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -937,7 +942,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -946,7 +951,7 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -967,28 +972,28 @@
     <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1101,11 +1106,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1115,6 +1120,27 @@
     <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11405,43 +11431,43 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>862393</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>862393</colOff>
+      <row>5</row>
+      <rowOff>131445</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11743,23 +11769,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" style="67" min="1" max="1"/>
-    <col width="13" customWidth="1" style="67" min="2" max="3"/>
-    <col width="13" customWidth="1" style="67" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="67" min="4" max="4"/>
+    <col width="15.77734375" customWidth="1" style="67" min="2" max="2"/>
+    <col width="25.77734375" customWidth="1" style="67" min="3" max="3"/>
+    <col width="25.77734375" customWidth="1" style="67" min="4" max="4"/>
     <col width="10" customWidth="1" style="67" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="67" min="6" max="6"/>
     <col width="11" customWidth="1" style="67" min="7" max="7"/>
-    <col width="15.77734375" customWidth="1" style="67" min="8" max="8"/>
-    <col width="10" customWidth="1" style="67" min="9" max="9"/>
+    <col width="20.77734375" customWidth="1" style="67" min="8" max="8"/>
+    <col width="15.77734375" customWidth="1" style="67" min="9" max="9"/>
     <col width="15.77734375" customWidth="1" style="67" min="10" max="10"/>
-    <col width="12" customWidth="1" style="67" min="11" max="11"/>
-    <col width="13" customWidth="1" style="67" min="12" max="12"/>
+    <col width="15.77734375" customWidth="1" style="67" min="11" max="11"/>
+    <col width="15.77734375" customWidth="1" style="67" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="67">
@@ -11807,7 +11834,7 @@
         </is>
       </c>
       <c r="I5" s="29" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="188" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
@@ -11826,7 +11853,7 @@
         </is>
       </c>
       <c r="I6" s="29" t="n"/>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" s="188" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
@@ -11845,7 +11872,7 @@
       <c r="G7" s="68" t="n"/>
       <c r="H7" s="68" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" s="188" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
@@ -11864,7 +11891,7 @@
       <c r="G8" s="68" t="n"/>
       <c r="H8" s="68" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="188" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
@@ -11877,7 +11904,7 @@
       <c r="L8" s="32" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="67">
-      <c r="A9" s="121" t="inlineStr">
+      <c r="A9" s="189" t="inlineStr">
         <is>
           <t>Se arma solo con las órdenes de compra y las entradas a almacén: pedido menos recibido</t>
         </is>
@@ -11913,7 +11940,7 @@
       <c r="L10" s="17" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="67">
-      <c r="A11" s="122" t="inlineStr">
+      <c r="A11" s="190" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
@@ -11924,7 +11951,7 @@
       <c r="E11" s="162" t="n"/>
       <c r="F11" s="162" t="n"/>
       <c r="G11" s="163" t="n"/>
-      <c r="H11" s="122" t="inlineStr">
+      <c r="H11" s="190" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
@@ -11935,7 +11962,7 @@
       <c r="L11" s="163" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="67">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="190" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
         </is>
@@ -11946,7 +11973,7 @@
       <c r="E12" s="162" t="n"/>
       <c r="F12" s="162" t="n"/>
       <c r="G12" s="163" t="n"/>
-      <c r="H12" s="122" t="inlineStr">
+      <c r="H12" s="190" t="inlineStr">
         <is>
           <t>Hoja N°</t>
         </is>
@@ -11975,62 +12002,62 @@
       <c r="L13" s="17" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1" s="67">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="191" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B14" s="124" t="inlineStr">
+      <c r="B14" s="192" t="inlineStr">
         <is>
           <t>Orden N°</t>
         </is>
       </c>
-      <c r="C14" s="124" t="inlineStr">
+      <c r="C14" s="192" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="D14" s="124" t="inlineStr">
+      <c r="D14" s="192" t="inlineStr">
         <is>
           <t>Material o servicio</t>
         </is>
       </c>
-      <c r="E14" s="124" t="inlineStr">
+      <c r="E14" s="192" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="F14" s="124" t="inlineStr">
+      <c r="F14" s="192" t="inlineStr">
         <is>
           <t>Pedido</t>
         </is>
       </c>
-      <c r="G14" s="124" t="inlineStr">
+      <c r="G14" s="192" t="inlineStr">
         <is>
           <t>Recibido</t>
         </is>
       </c>
-      <c r="H14" s="124" t="inlineStr">
+      <c r="H14" s="192" t="inlineStr">
         <is>
           <t>Saldo</t>
         </is>
       </c>
-      <c r="I14" s="124" t="inlineStr">
+      <c r="I14" s="192" t="inlineStr">
         <is>
           <t>Entrega prometida</t>
         </is>
       </c>
-      <c r="J14" s="124" t="inlineStr">
+      <c r="J14" s="192" t="inlineStr">
         <is>
           <t>Días de atraso</t>
         </is>
       </c>
-      <c r="K14" s="124" t="inlineStr">
+      <c r="K14" s="192" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="L14" s="124" t="inlineStr">
+      <c r="L14" s="192" t="inlineStr">
         <is>
           <t>Gestión con el proveedor</t>
         </is>
@@ -12535,7 +12562,7 @@
       <c r="L45" s="17" t="n"/>
     </row>
     <row r="46" ht="45" customHeight="1" s="67">
-      <c r="A46" s="122" t="inlineStr">
+      <c r="A46" s="190" t="inlineStr">
         <is>
           <t>Observaciones y acciones a tomar</t>
         </is>
@@ -12571,7 +12598,7 @@
       <c r="L47" s="17" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1" s="67">
-      <c r="A48" s="130" t="inlineStr">
+      <c r="A48" s="193" t="inlineStr">
         <is>
           <t>ELABORA — COMPRAS</t>
         </is>
@@ -12581,7 +12608,7 @@
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
       <c r="F48" s="32" t="n"/>
-      <c r="G48" s="130" t="inlineStr">
+      <c r="G48" s="193" t="inlineStr">
         <is>
           <t>REVISA — DIRECTOR DE OBRA</t>
         </is>
@@ -12593,7 +12620,7 @@
       <c r="L48" s="32" t="n"/>
     </row>
     <row r="49" ht="42" customHeight="1" s="67">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="194" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12603,7 +12630,7 @@
       <c r="D49" s="171" t="n"/>
       <c r="E49" s="171" t="n"/>
       <c r="F49" s="172" t="n"/>
-      <c r="G49" s="18" t="inlineStr">
+      <c r="G49" s="194" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12615,7 +12642,7 @@
       <c r="L49" s="172" t="n"/>
     </row>
     <row r="50" ht="21" customHeight="1" s="67">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="194" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12625,7 +12652,7 @@
       <c r="D50" s="171" t="n"/>
       <c r="E50" s="171" t="n"/>
       <c r="F50" s="172" t="n"/>
-      <c r="G50" s="18" t="inlineStr">
+      <c r="G50" s="194" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12637,7 +12664,7 @@
       <c r="L50" s="172" t="n"/>
     </row>
     <row r="51" ht="21" customHeight="1" s="67">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="194" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12647,7 +12674,7 @@
       <c r="D51" s="171" t="n"/>
       <c r="E51" s="171" t="n"/>
       <c r="F51" s="172" t="n"/>
-      <c r="G51" s="18" t="inlineStr">
+      <c r="G51" s="194" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12687,44 +12714,44 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="38">
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="D1:L2"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="C46:L46"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="G48:L48"/>
-    <mergeCell ref="K6:L6"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="I51:L51"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="D1:L2"/>
+    <mergeCell ref="C49:F49"/>
     <mergeCell ref="A47:L47"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="D3:L3"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="C49:F49"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="I49:L49"/>
     <mergeCell ref="A50:B50"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="H11:I11"/>
     <mergeCell ref="A10:L10"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="A45:L45"/>
+    <mergeCell ref="G48:L48"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="C46:L46"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
